--- a/artfynd/A 11803-2022 artfynd.xlsx
+++ b/artfynd/A 11803-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11803-2022 artfynd.xlsx
+++ b/artfynd/A 11803-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72870849</v>
+        <v>72870848</v>
       </c>
       <c r="B2" t="n">
-        <v>99590</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221333</v>
+        <v>220164</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Backklöver</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium montanum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hanmora, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640937.1300085358</v>
+        <v>640937</v>
       </c>
       <c r="R2" t="n">
-        <v>6584650.822081438</v>
+        <v>6584651</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +747,9 @@
           <t>2018-07-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-07-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,54 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72870848</v>
+        <v>72870847</v>
       </c>
       <c r="B3" t="n">
-        <v>101691</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hanmora, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640937.1300085358</v>
+        <v>640937</v>
       </c>
       <c r="R3" t="n">
-        <v>6584650.822081438</v>
+        <v>6584651</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,19 +854,9 @@
           <t>2018-07-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-07-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +865,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,32 +892,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>72870847</v>
+        <v>72870849</v>
       </c>
       <c r="B4" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>221333</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Trifolium montanum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -962,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640937.1300085358</v>
+        <v>640937</v>
       </c>
       <c r="R4" t="n">
-        <v>6584650.822081438</v>
+        <v>6584651</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,19 +960,9 @@
           <t>2018-07-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-07-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
